--- a/event_planner_forms/010_tournament_award_ribbon_color_choice_order_form--event_planner_forms.xlsx
+++ b/event_planner_forms/010_tournament_award_ribbon_color_choice_order_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tournament_award_ribbon_choice_order_form</t>
+          <t>tournament_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tournament Award Ribbon Choice Order Form</t>
+          <t>Tournament Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>quantity_1</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Award Color</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>color_1</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>color</t>
+          <t>Quantity of Winners</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>quantity_2</t>
+          <t>payment_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Payment Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>payment_type_1</t>
+          <t>payment_amount</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>payment type</t>
+          <t>Payment Amount</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>quantity_3</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>quantity</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>payment_amount_1</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>payment amount</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>payment_terms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Payment Terms</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>email_1</t>
+          <t>confirm_payment_terms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Confirm Payment Terms</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>confirm_email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Confirm Email</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone_1</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>payment_method_details</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Payment Method Details</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,44 +791,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>payment_method_details2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>payment terms</t>
+          <t>Payment Method Details 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>payment_terms</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>payment terms</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -873,7 +850,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>color_1_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -890,7 +867,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>color_1_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -907,7 +884,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>color_1_choices</t>
+          <t>color_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -924,7 +901,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>payment_type_1_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -941,7 +918,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>payment_type_1_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -958,7 +935,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_type_1_choices</t>
+          <t>payment_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1009,7 +986,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>payment_terms_choices</t>
+          <t>confirm_payment_terms_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1026,7 +1003,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>payment_terms_choices</t>
+          <t>confirm_payment_terms_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1037,6 +1014,40 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>payment_method_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>payment_method_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Option B</t>
         </is>
       </c>
     </row>
